--- a/rmd/Daten/excel_spalte_new.xlsx
+++ b/rmd/Daten/excel_spalte_new.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="2020_2025" sheetId="5" r:id="rId1"/>
